--- a/RAMON FRANCO/Septiembre/PRORRATEO-RAMON-FRANCO-Septiembre.xlsx
+++ b/RAMON FRANCO/Septiembre/PRORRATEO-RAMON-FRANCO-Septiembre.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\RAMON FRANCO\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\RAMON FRANCO\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1FE9381-EED2-41AC-9DED-2A0EA5F193E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D3C8885-400E-4B39-B19E-7F408C763104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Planilla" sheetId="1" r:id="rId1"/>
     <sheet name="TSG" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Planilla!$A$1:$Q$32</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -26,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="85">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -82,9 +85,6 @@
     <t>SALDO MES ANTERIOR</t>
   </si>
   <si>
-    <t>Total a Pagar</t>
-  </si>
-  <si>
     <t>CAROLINA CANCIANI</t>
   </si>
   <si>
@@ -271,10 +271,19 @@
     <t>GISELA</t>
   </si>
   <si>
-    <t>EXPENSAS - VENCIMIENTO 15/09 LIQUIDACION: AGOSTO</t>
-  </si>
-  <si>
     <t>SERGIO</t>
+  </si>
+  <si>
+    <t>EXPENSAS - VENCIMIENTO 15/10 LIQUIDACION: SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>Total a Pagar 2do vto</t>
+  </si>
+  <si>
+    <t>Total a Pagar 1er vto</t>
+  </si>
+  <si>
+    <t>Vto: 14/10</t>
   </si>
 </sst>
 </file>
@@ -282,12 +291,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;\ #,##0;[Red]\-&quot;$&quot;\ #,##0"/>
-    <numFmt numFmtId="165" formatCode="_-&quot;$&quot;\ * #,##0.00_-;\-&quot;$&quot;\ * #,##0.00_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.0000_-;\-* #,##0.0000_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="17" x14ac:knownFonts="1">
     <font>
@@ -672,17 +681,17 @@
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -696,32 +705,32 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="9" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -736,16 +745,16 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="2" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="7" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="2" fillId="2" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -757,39 +766,39 @@
     </xf>
     <xf numFmtId="43" fontId="8" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="43" fontId="10" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="10" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="6" fontId="2" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="2" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="11" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="11" fillId="2" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="11" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="11" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="2" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -798,10 +807,20 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="16" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="16" fillId="2" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="10" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -835,7 +854,7 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -853,14 +872,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="10" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="12" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -1203,7 +1214,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P37"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="6" hidden="1" customWidth="1"/>
@@ -1220,31 +1231,32 @@
     <col min="12" max="12" width="9.28515625" customWidth="1"/>
     <col min="13" max="13" width="10.42578125" customWidth="1"/>
     <col min="14" max="14" width="10" customWidth="1"/>
-    <col min="15" max="15" width="11.140625" customWidth="1"/>
-    <col min="16" max="16" width="12.140625" customWidth="1"/>
+    <col min="15" max="16" width="11.140625" customWidth="1"/>
+    <col min="17" max="17" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="74" t="s">
+    <row r="1" spans="1:17" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="82" t="s">
         <v>81</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
-      <c r="J1" s="75"/>
-      <c r="K1" s="75"/>
-      <c r="L1" s="75"/>
-      <c r="M1" s="75"/>
-      <c r="N1" s="75"/>
-      <c r="O1" s="75"/>
-      <c r="P1" s="76"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="83"/>
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="J1" s="83"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="83"/>
+      <c r="M1" s="83"/>
+      <c r="N1" s="83"/>
+      <c r="O1" s="83"/>
+      <c r="P1" s="83"/>
+      <c r="Q1" s="84"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="9"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
@@ -1252,9 +1264,9 @@
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
       <c r="K2" s="21"/>
-      <c r="P2" s="8"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q2" s="8"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>0</v>
       </c>
@@ -1264,11 +1276,11 @@
       <c r="I3" s="4"/>
       <c r="K3" s="11"/>
       <c r="L3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P3" s="8"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="Q3" s="8"/>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>1</v>
       </c>
@@ -1277,15 +1289,16 @@
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
       <c r="K4" s="11"/>
-      <c r="L4" s="72">
+      <c r="L4" s="80">
         <v>1153202676</v>
       </c>
-      <c r="M4" s="72"/>
-      <c r="N4" s="72"/>
-      <c r="O4" s="72"/>
-      <c r="P4" s="73"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M4" s="80"/>
+      <c r="N4" s="80"/>
+      <c r="O4" s="80"/>
+      <c r="P4" s="80"/>
+      <c r="Q4" s="81"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>15</v>
       </c>
@@ -1298,14 +1311,14 @@
       <c r="I5" s="4"/>
       <c r="K5" s="11"/>
       <c r="L5" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="P5" s="8"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+      <c r="Q5" s="8"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="10"/>
       <c r="C6" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D6" s="21"/>
       <c r="F6" s="4"/>
@@ -1314,13 +1327,13 @@
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
-      <c r="P6" s="8"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q6" s="8"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="10"/>
       <c r="B7" s="25"/>
       <c r="C7" s="26">
-        <v>958293.75</v>
+        <v>705459.15999999992</v>
       </c>
       <c r="D7" s="26"/>
       <c r="F7" s="4"/>
@@ -1329,12 +1342,12 @@
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
-      <c r="P7" s="8"/>
-    </row>
-    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Q7" s="8"/>
+    </row>
+    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10"/>
       <c r="B8" s="25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" s="25">
         <v>0</v>
@@ -1346,13 +1359,13 @@
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
-      <c r="P8" s="8"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q8" s="8"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="10"/>
       <c r="B9" s="25"/>
       <c r="C9" s="25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D9" s="25"/>
       <c r="F9" s="4"/>
@@ -1361,13 +1374,13 @@
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
-      <c r="P9" s="8"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q9" s="8"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="15"/>
       <c r="B10" s="16"/>
       <c r="C10" s="51">
-        <v>700000</v>
+        <v>350000</v>
       </c>
       <c r="D10" s="51"/>
       <c r="E10" s="38"/>
@@ -1381,9 +1394,12 @@
       <c r="M10" s="17"/>
       <c r="N10" s="17"/>
       <c r="O10" s="17"/>
-      <c r="P10" s="19"/>
-    </row>
-    <row r="11" spans="1:16" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P10" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q10" s="19"/>
+    </row>
+    <row r="11" spans="1:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
         <v>2</v>
       </c>
@@ -1394,97 +1410,104 @@
         <v>3</v>
       </c>
       <c r="D11" s="63" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E11" s="39" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F11" s="14" t="s">
         <v>17</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H11" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="J11" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="I11" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="J11" s="14" t="s">
-        <v>72</v>
-      </c>
       <c r="K11" s="14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L11" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M11" s="13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N11" s="13" t="s">
         <v>16</v>
       </c>
       <c r="O11" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P11" s="13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+      <c r="Q11" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7">
         <v>1</v>
       </c>
-      <c r="B12" s="88" t="s">
+      <c r="B12" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="89" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="89"/>
-      <c r="E12" s="90">
+      <c r="C12" s="72" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="72"/>
+      <c r="E12" s="73">
         <v>7.99</v>
       </c>
-      <c r="F12" s="91">
-        <v>222026.96665235999</v>
-      </c>
-      <c r="G12" s="92">
-        <v>0</v>
-      </c>
-      <c r="H12" s="91"/>
-      <c r="I12" s="92" t="e">
+      <c r="F12" s="74">
+        <v>372286.79460954876</v>
+      </c>
+      <c r="G12" s="75">
+        <v>0</v>
+      </c>
+      <c r="H12" s="74"/>
+      <c r="I12" s="75" t="e">
         <f>C9*E12/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J12" s="92">
-        <f>F12-G12-H12</f>
-        <v>222026.96665235999</v>
-      </c>
-      <c r="K12" s="92"/>
-      <c r="L12" s="93">
+      <c r="J12" s="75">
+        <f t="shared" ref="J12:J19" si="0">F12-G12-H12</f>
+        <v>372286.79460954876</v>
+      </c>
+      <c r="K12" s="75"/>
+      <c r="L12" s="76">
         <f>IF(J11&gt;0,(J12+K12)*8%,0)</f>
-        <v>17762.157332188799</v>
-      </c>
-      <c r="M12" s="93">
+        <v>29782.943568763902</v>
+      </c>
+      <c r="M12" s="76">
         <f>J12+L12+K12</f>
-        <v>239789.12398454879</v>
-      </c>
-      <c r="N12" s="92">
+        <v>402069.73817831266</v>
+      </c>
+      <c r="N12" s="75">
         <f>C7*E12/100</f>
-        <v>76567.670624999999</v>
-      </c>
-      <c r="O12" s="92">
-        <f>C$10*E12/100</f>
-        <v>55930</v>
-      </c>
-      <c r="P12" s="93">
+        <v>56366.186883999995</v>
+      </c>
+      <c r="O12" s="75">
+        <f t="shared" ref="O12:O29" si="1">C$10*E12/100</f>
+        <v>27965</v>
+      </c>
+      <c r="P12" s="75">
         <f>N12+M12+O12</f>
-        <v>372286.79460954876</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>486400.92506231263</v>
+      </c>
+      <c r="Q12" s="76">
+        <f>P12*3%+P12</f>
+        <v>500992.95281418203</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7">
         <v>2</v>
       </c>
@@ -1492,30 +1515,30 @@
         <v>6</v>
       </c>
       <c r="C13" s="64" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13" s="64" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E13" s="43">
         <v>6.05</v>
       </c>
       <c r="F13" s="58">
-        <v>75722.996085000006</v>
+        <v>100326.77187500001</v>
       </c>
       <c r="G13" s="44">
         <v>0</v>
       </c>
       <c r="H13" s="69">
-        <f>F13</f>
-        <v>75722.996085000006</v>
+        <f t="shared" ref="H13:H18" si="2">F13</f>
+        <v>100326.77187500001</v>
       </c>
       <c r="I13" s="44" t="e">
         <f>C9*E13/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="J13" s="44">
-        <f>F13-G13-H13</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K13" s="44"/>
@@ -1524,23 +1547,27 @@
         <v>0</v>
       </c>
       <c r="M13" s="45">
-        <f t="shared" ref="M13:M15" si="0">J13+L13+K13</f>
+        <f t="shared" ref="M13:M15" si="3">J13+L13+K13</f>
         <v>0</v>
       </c>
       <c r="N13" s="44">
         <f>C7*E13/100</f>
-        <v>57976.771874999999</v>
+        <v>42680.279179999998</v>
       </c>
       <c r="O13" s="44">
-        <f>C$10*E13/100</f>
-        <v>42350</v>
-      </c>
-      <c r="P13" s="45">
-        <f t="shared" ref="P13:P29" si="1">N13+M13+O13</f>
-        <v>100326.77187500001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>21175</v>
+      </c>
+      <c r="P13" s="77">
+        <f t="shared" ref="P13:P29" si="4">N13+M13+O13</f>
+        <v>63855.279179999998</v>
+      </c>
+      <c r="Q13" s="78">
+        <f t="shared" ref="Q13:Q29" si="5">P13*3%+P13</f>
+        <v>65770.9375554</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7">
         <v>3</v>
       </c>
@@ -1548,55 +1575,59 @@
         <v>8</v>
       </c>
       <c r="C14" s="64" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D14" s="64" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E14" s="43">
         <v>6.02</v>
       </c>
       <c r="F14" s="58">
-        <v>75347.510154000003</v>
+        <v>99829.283750000002</v>
       </c>
       <c r="G14" s="44">
         <v>0</v>
       </c>
       <c r="H14" s="69">
-        <f>F14</f>
-        <v>75347.510154000003</v>
+        <f t="shared" si="2"/>
+        <v>99829.283750000002</v>
       </c>
       <c r="I14" s="44" t="e">
         <f>C9*E14/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="J14" s="44">
-        <f>F14-G14-H14</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K14" s="44"/>
       <c r="L14" s="45">
-        <f t="shared" ref="L14:L29" si="2">(J14+K14)*8%</f>
+        <f t="shared" ref="L14:L29" si="6">(J14+K14)*8%</f>
         <v>0</v>
       </c>
       <c r="M14" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N14" s="44">
         <f>C7*E14/100</f>
-        <v>57689.283750000002</v>
+        <v>42468.641431999989</v>
       </c>
       <c r="O14" s="44">
-        <f>C$10*E14/100</f>
-        <v>42140</v>
-      </c>
-      <c r="P14" s="45">
         <f t="shared" si="1"/>
-        <v>99829.283750000002</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>21070</v>
+      </c>
+      <c r="P14" s="77">
+        <f t="shared" si="4"/>
+        <v>63538.641431999989</v>
+      </c>
+      <c r="Q14" s="78">
+        <f t="shared" si="5"/>
+        <v>65444.800674959988</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="7">
         <v>4</v>
       </c>
@@ -1604,51 +1635,55 @@
         <v>7</v>
       </c>
       <c r="C15" s="64" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D15" s="65"/>
       <c r="E15" s="49">
         <v>7.63</v>
       </c>
       <c r="F15" s="60">
-        <v>212023.24850532002</v>
+        <v>126527.813125</v>
       </c>
       <c r="G15" s="46"/>
       <c r="H15" s="69">
-        <f>F15</f>
-        <v>212023.24850532002</v>
+        <f t="shared" si="2"/>
+        <v>126527.813125</v>
       </c>
       <c r="I15" s="44" t="e">
         <f>C9*E15/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="J15" s="44">
-        <f>F15-G15-H15</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K15" s="48"/>
       <c r="L15" s="45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M15" s="45">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N15" s="50">
         <f>C7*E15/100</f>
-        <v>73117.813125000001</v>
+        <v>53826.53390799999</v>
       </c>
       <c r="O15" s="44">
-        <f>C$10*E15/100</f>
-        <v>53410</v>
-      </c>
-      <c r="P15" s="45">
         <f t="shared" si="1"/>
-        <v>126527.813125</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>26705</v>
+      </c>
+      <c r="P15" s="77">
+        <f t="shared" si="4"/>
+        <v>80531.533907999983</v>
+      </c>
+      <c r="Q15" s="78">
+        <f t="shared" si="5"/>
+        <v>82947.479925239983</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <v>6</v>
       </c>
@@ -1656,35 +1691,35 @@
         <v>9</v>
       </c>
       <c r="C16" s="64" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" s="64" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E16" s="43">
         <v>6.05</v>
       </c>
       <c r="F16" s="58">
-        <v>75722.996085000006</v>
+        <v>100326.77187500001</v>
       </c>
       <c r="G16" s="46">
         <v>0</v>
       </c>
       <c r="H16" s="69">
-        <f>F16</f>
-        <v>75722.996085000006</v>
+        <f t="shared" si="2"/>
+        <v>100326.77187500001</v>
       </c>
       <c r="I16" s="44" t="e">
         <f>C9*E16/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="J16" s="44">
-        <f>F16-G16-H16</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K16" s="44"/>
       <c r="L16" s="45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M16" s="45">
@@ -1693,18 +1728,22 @@
       </c>
       <c r="N16" s="44">
         <f>C7*E16/100</f>
-        <v>57976.771874999999</v>
+        <v>42680.279179999998</v>
       </c>
       <c r="O16" s="44">
-        <f>C$10*E16/100</f>
-        <v>42350</v>
-      </c>
-      <c r="P16" s="45">
         <f t="shared" si="1"/>
-        <v>100326.77187500001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>21175</v>
+      </c>
+      <c r="P16" s="77">
+        <f t="shared" si="4"/>
+        <v>63855.279179999998</v>
+      </c>
+      <c r="Q16" s="78">
+        <f t="shared" si="5"/>
+        <v>65770.9375554</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
         <v>7</v>
       </c>
@@ -1712,55 +1751,59 @@
         <v>10</v>
       </c>
       <c r="C17" s="64" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D17" s="64" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E17" s="43">
         <v>6.02</v>
       </c>
       <c r="F17" s="58">
-        <v>75347.510154000003</v>
+        <v>99829.283750000002</v>
       </c>
       <c r="G17" s="44">
         <v>0</v>
       </c>
       <c r="H17" s="69">
-        <f>F17</f>
-        <v>75347.510154000003</v>
+        <f t="shared" si="2"/>
+        <v>99829.283750000002</v>
       </c>
       <c r="I17" s="44" t="e">
         <f>C9*E17/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="J17" s="44">
-        <f>F17-G17-H17</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K17" s="44"/>
       <c r="L17" s="45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M17" s="45">
-        <f t="shared" ref="M17:M29" si="3">J17+L17+K17</f>
+        <f t="shared" ref="M17:M29" si="7">J17+L17+K17</f>
         <v>0</v>
       </c>
       <c r="N17" s="44">
         <f>C7*E17/100</f>
-        <v>57689.283750000002</v>
+        <v>42468.641431999989</v>
       </c>
       <c r="O17" s="44">
-        <f>C$10*E17/100</f>
-        <v>42140</v>
-      </c>
-      <c r="P17" s="45">
         <f t="shared" si="1"/>
-        <v>99829.283750000002</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>21070</v>
+      </c>
+      <c r="P17" s="77">
+        <f t="shared" si="4"/>
+        <v>63538.641431999989</v>
+      </c>
+      <c r="Q17" s="78">
+        <f t="shared" si="5"/>
+        <v>65444.800674959988</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
         <v>8</v>
       </c>
@@ -1768,53 +1811,57 @@
         <v>11</v>
       </c>
       <c r="C18" s="64" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" s="64"/>
       <c r="E18" s="43">
         <v>7.63</v>
       </c>
       <c r="F18" s="58">
-        <v>95498.588451000003</v>
+        <v>126527.813125</v>
       </c>
       <c r="G18" s="44">
         <v>0</v>
       </c>
       <c r="H18" s="69">
-        <f>F18</f>
-        <v>95498.588451000003</v>
+        <f t="shared" si="2"/>
+        <v>126527.813125</v>
       </c>
       <c r="I18" s="44" t="e">
         <f>C9*E18/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="J18" s="44">
-        <f>F18-G18-H18</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K18" s="44"/>
       <c r="L18" s="45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M18" s="45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="N18" s="44">
         <f>C7*E18/100</f>
-        <v>73117.813125000001</v>
+        <v>53826.53390799999</v>
       </c>
       <c r="O18" s="44">
-        <f>C$10*E18/100</f>
-        <v>53410</v>
-      </c>
-      <c r="P18" s="45">
         <f t="shared" si="1"/>
-        <v>126527.813125</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>26705</v>
+      </c>
+      <c r="P18" s="77">
+        <f t="shared" si="4"/>
+        <v>80531.533907999983</v>
+      </c>
+      <c r="Q18" s="78">
+        <f t="shared" si="5"/>
+        <v>82947.479925239983</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7">
         <v>9</v>
       </c>
@@ -1822,14 +1869,14 @@
         <v>12</v>
       </c>
       <c r="C19" s="64" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D19" s="64"/>
       <c r="E19" s="43">
         <v>6.05</v>
       </c>
       <c r="F19" s="58">
-        <v>75722.996085000006</v>
+        <v>182107.6076468</v>
       </c>
       <c r="G19" s="44">
         <v>0</v>
@@ -1840,54 +1887,58 @@
         <v>#VALUE!</v>
       </c>
       <c r="J19" s="44">
-        <f>F19-G19-H19</f>
-        <v>75722.996085000006</v>
+        <f t="shared" si="0"/>
+        <v>182107.6076468</v>
       </c>
       <c r="K19" s="44"/>
       <c r="L19" s="45">
-        <f t="shared" si="2"/>
-        <v>6057.8396868000009</v>
+        <f t="shared" si="6"/>
+        <v>14568.608611743999</v>
       </c>
       <c r="M19" s="45">
-        <f t="shared" si="3"/>
-        <v>81780.835771800004</v>
+        <f t="shared" si="7"/>
+        <v>196676.21625854401</v>
       </c>
       <c r="N19" s="44">
         <f>C7*E19/100</f>
-        <v>57976.771874999999</v>
+        <v>42680.279179999998</v>
       </c>
       <c r="O19" s="44">
-        <f>C$10*E19/100</f>
-        <v>42350</v>
-      </c>
-      <c r="P19" s="45">
-        <f>N19+M19+O19</f>
-        <v>182107.6076468</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>21175</v>
+      </c>
+      <c r="P19" s="77">
+        <f t="shared" si="4"/>
+        <v>260531.49543854402</v>
+      </c>
+      <c r="Q19" s="78">
+        <f t="shared" si="5"/>
+        <v>268347.44030170032</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7">
         <v>10</v>
       </c>
       <c r="B20" s="52" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20" s="64" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D20" s="64"/>
       <c r="E20" s="43">
         <v>6.02</v>
       </c>
       <c r="F20" s="58">
-        <v>75347.510154000003</v>
+        <v>45829.283750000002</v>
       </c>
       <c r="G20" s="44">
         <v>0</v>
       </c>
       <c r="H20" s="69">
-        <f>F20+50000</f>
-        <v>125347.510154</v>
+        <f>F20</f>
+        <v>45829.283750000002</v>
       </c>
       <c r="I20" s="44" t="e">
         <f>C9*E20/100</f>
@@ -1896,368 +1947,395 @@
       <c r="J20" s="44"/>
       <c r="K20" s="44">
         <f>F20-H20</f>
-        <v>-50000</v>
+        <v>0</v>
       </c>
       <c r="L20" s="45">
         <f>IF(J19&gt;0,(J20+K20)*8%,0)</f>
-        <v>-4000</v>
+        <v>0</v>
       </c>
       <c r="M20" s="45">
-        <f t="shared" si="3"/>
-        <v>-54000</v>
+        <f t="shared" si="7"/>
+        <v>0</v>
       </c>
       <c r="N20" s="44">
         <f>C7*E20/100</f>
-        <v>57689.283750000002</v>
+        <v>42468.641431999989</v>
       </c>
       <c r="O20" s="44">
-        <f>C$10*E20/100</f>
-        <v>42140</v>
-      </c>
-      <c r="P20" s="45">
-        <f>N20+M20+O20</f>
-        <v>45829.283750000002</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>21070</v>
+      </c>
+      <c r="P20" s="77">
+        <f t="shared" si="4"/>
+        <v>63538.641431999989</v>
+      </c>
+      <c r="Q20" s="78">
+        <f t="shared" si="5"/>
+        <v>65444.800674959988</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7">
         <v>11</v>
       </c>
       <c r="B21" s="52" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C21" s="66" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D21" s="66"/>
       <c r="E21" s="43">
         <v>21.2</v>
       </c>
       <c r="F21" s="58">
-        <v>265343.39123999997</v>
+        <v>351558.27500000002</v>
       </c>
       <c r="G21" s="44">
         <v>0</v>
       </c>
       <c r="H21" s="69">
         <f>F21</f>
-        <v>265343.39123999997</v>
+        <v>351558.27500000002</v>
       </c>
       <c r="I21" s="44" t="e">
         <f>C9*E21/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="J21" s="44">
-        <f>F21-G21-H21</f>
+        <f t="shared" ref="J21:J29" si="8">F21-G21-H21</f>
         <v>0</v>
       </c>
       <c r="K21" s="44"/>
       <c r="L21" s="45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M21" s="45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="N21" s="44">
         <f>C7*E21/100</f>
-        <v>203158.27499999999</v>
+        <v>149557.34191999998</v>
       </c>
       <c r="O21" s="44">
-        <f>C$10*E21/100</f>
-        <v>148400</v>
-      </c>
-      <c r="P21" s="45">
         <f t="shared" si="1"/>
-        <v>351558.27500000002</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>74200</v>
+      </c>
+      <c r="P21" s="77">
+        <f t="shared" si="4"/>
+        <v>223757.34191999998</v>
+      </c>
+      <c r="Q21" s="78">
+        <f t="shared" si="5"/>
+        <v>230470.06217759999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="7">
         <v>12</v>
       </c>
       <c r="B22" s="52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C22" s="66" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D22" s="66" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E22" s="43">
         <v>6.81</v>
       </c>
       <c r="F22" s="58">
-        <v>85235.306337000002</v>
+        <v>112929.80437500001</v>
       </c>
       <c r="G22" s="44">
         <v>0</v>
       </c>
       <c r="H22" s="69">
         <f>F22</f>
-        <v>85235.306337000002</v>
+        <v>112929.80437500001</v>
       </c>
       <c r="I22" s="44" t="e">
         <f>C9*E22/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="J22" s="44">
-        <f>F22-G22-H22</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K22" s="44"/>
       <c r="L22" s="45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M22" s="45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="N22" s="44">
         <f>C7*E22/100</f>
-        <v>65259.804375</v>
+        <v>48041.768795999989</v>
       </c>
       <c r="O22" s="44">
-        <f>C$10*E22/100</f>
-        <v>47670</v>
-      </c>
-      <c r="P22" s="45">
         <f t="shared" si="1"/>
-        <v>112929.80437500001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>23835</v>
+      </c>
+      <c r="P22" s="77">
+        <f t="shared" si="4"/>
+        <v>71876.768795999989</v>
+      </c>
+      <c r="Q22" s="78">
+        <f t="shared" si="5"/>
+        <v>74033.071859879987</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7">
         <v>13</v>
       </c>
       <c r="B23" s="52" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C23" s="64" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D23" s="64" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E23" s="43">
         <v>6.52</v>
       </c>
       <c r="F23" s="69">
-        <v>81605.609003999998</v>
+        <v>108120.7525</v>
       </c>
       <c r="G23" s="44">
         <v>0</v>
       </c>
       <c r="H23" s="69">
-        <f>F23</f>
-        <v>81605.609003999998</v>
+        <v>62481</v>
       </c>
       <c r="I23" s="44">
         <v>0</v>
       </c>
       <c r="J23" s="44">
-        <f>F23-G23-H23</f>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>45639.752500000002</v>
       </c>
       <c r="K23" s="44"/>
       <c r="L23" s="67">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="6"/>
+        <v>3651.1802000000002</v>
       </c>
       <c r="M23" s="67">
         <f>J23+L23+K23</f>
-        <v>0</v>
+        <v>49290.932700000005</v>
       </c>
       <c r="N23" s="44">
         <f>C7*E23/100</f>
-        <v>62480.752500000002</v>
+        <v>45995.937231999989</v>
       </c>
       <c r="O23" s="44">
-        <f>C$10*E23/100</f>
-        <v>45640</v>
-      </c>
-      <c r="P23" s="45">
         <f t="shared" si="1"/>
-        <v>108120.7525</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>22820</v>
+      </c>
+      <c r="P23" s="77">
+        <f t="shared" si="4"/>
+        <v>118106.869932</v>
+      </c>
+      <c r="Q23" s="78">
+        <f t="shared" si="5"/>
+        <v>121650.07602996001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
         <v>14</v>
       </c>
-      <c r="B24" s="88" t="s">
-        <v>56</v>
-      </c>
-      <c r="C24" s="89" t="s">
-        <v>44</v>
-      </c>
-      <c r="D24" s="89"/>
-      <c r="E24" s="90">
+      <c r="B24" s="71" t="s">
+        <v>55</v>
+      </c>
+      <c r="C24" s="72" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" s="72"/>
+      <c r="E24" s="73">
         <v>1.18</v>
       </c>
-      <c r="F24" s="91">
-        <v>530501.03312079341</v>
-      </c>
-      <c r="G24" s="92">
-        <v>0</v>
-      </c>
-      <c r="H24" s="91"/>
-      <c r="I24" s="92" t="e">
+      <c r="F24" s="74">
+        <v>592508.98202045681</v>
+      </c>
+      <c r="G24" s="75">
+        <v>0</v>
+      </c>
+      <c r="H24" s="74"/>
+      <c r="I24" s="75" t="e">
         <f>C9*E24/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J24" s="92">
-        <f>F24-G24-H24</f>
-        <v>530501.03312079341</v>
-      </c>
-      <c r="K24" s="92"/>
-      <c r="L24" s="93">
-        <f t="shared" si="2"/>
-        <v>42440.082649663476</v>
-      </c>
-      <c r="M24" s="93">
-        <f t="shared" si="3"/>
-        <v>572941.11577045685</v>
-      </c>
-      <c r="N24" s="92">
+      <c r="J24" s="75">
+        <f t="shared" si="8"/>
+        <v>592508.98202045681</v>
+      </c>
+      <c r="K24" s="75"/>
+      <c r="L24" s="76">
+        <f t="shared" si="6"/>
+        <v>47400.718561636546</v>
+      </c>
+      <c r="M24" s="76">
+        <f t="shared" si="7"/>
+        <v>639909.70058209333</v>
+      </c>
+      <c r="N24" s="75">
         <f>C7*E24/100</f>
-        <v>11307.866249999999</v>
-      </c>
-      <c r="O24" s="92">
-        <f>C$10*E24/100</f>
-        <v>8260</v>
-      </c>
-      <c r="P24" s="93">
+        <v>8324.4180879999985</v>
+      </c>
+      <c r="O24" s="75">
         <f t="shared" si="1"/>
-        <v>592508.98202045681</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4130</v>
+      </c>
+      <c r="P24" s="75">
+        <f t="shared" si="4"/>
+        <v>652364.11867009336</v>
+      </c>
+      <c r="Q24" s="76">
+        <f t="shared" si="5"/>
+        <v>671935.04223019618</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7">
         <v>15</v>
       </c>
-      <c r="B25" s="88" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="89" t="s">
-        <v>46</v>
-      </c>
-      <c r="D25" s="89"/>
-      <c r="E25" s="90">
+      <c r="B25" s="71" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" s="72" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" s="72"/>
+      <c r="E25" s="73">
         <v>1.17</v>
       </c>
-      <c r="F25" s="91">
-        <v>523675.87064790376</v>
-      </c>
-      <c r="G25" s="92">
-        <v>0</v>
-      </c>
-      <c r="H25" s="91">
-        <v>0</v>
-      </c>
-      <c r="I25" s="92" t="e">
+      <c r="F25" s="74">
+        <v>584971.97717473609</v>
+      </c>
+      <c r="G25" s="75">
+        <v>0</v>
+      </c>
+      <c r="H25" s="74">
+        <v>0</v>
+      </c>
+      <c r="I25" s="75" t="e">
         <f>C9*E25/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J25" s="92">
-        <f>F25-G25-H25</f>
-        <v>523675.87064790376</v>
-      </c>
-      <c r="K25" s="92"/>
-      <c r="L25" s="93">
-        <f t="shared" si="2"/>
-        <v>41894.069651832302</v>
-      </c>
-      <c r="M25" s="93">
-        <f t="shared" si="3"/>
-        <v>565569.9402997361</v>
-      </c>
-      <c r="N25" s="92">
+      <c r="J25" s="75">
+        <f t="shared" si="8"/>
+        <v>584971.97717473609</v>
+      </c>
+      <c r="K25" s="75"/>
+      <c r="L25" s="76">
+        <f t="shared" si="6"/>
+        <v>46797.758173978887</v>
+      </c>
+      <c r="M25" s="76">
+        <f t="shared" si="7"/>
+        <v>631769.73534871498</v>
+      </c>
+      <c r="N25" s="75">
         <f>C7*E25/100</f>
-        <v>11212.036875</v>
-      </c>
-      <c r="O25" s="92">
-        <f>C$10*E25/100</f>
-        <v>8190</v>
-      </c>
-      <c r="P25" s="93">
+        <v>8253.8721719999976</v>
+      </c>
+      <c r="O25" s="75">
         <f t="shared" si="1"/>
-        <v>584971.97717473609</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>4095</v>
+      </c>
+      <c r="P25" s="75">
+        <f t="shared" si="4"/>
+        <v>644118.60752071498</v>
+      </c>
+      <c r="Q25" s="76">
+        <f t="shared" si="5"/>
+        <v>663442.16574633645</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7">
         <v>16</v>
       </c>
       <c r="B26" s="52" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C26" s="64" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D26" s="64"/>
       <c r="E26" s="43">
         <v>1.06</v>
       </c>
       <c r="F26" s="58">
-        <v>13267.169562000001</v>
+        <v>17577.91375</v>
       </c>
       <c r="G26" s="44">
         <v>0</v>
       </c>
       <c r="H26" s="69">
         <f>F26</f>
-        <v>13267.169562000001</v>
+        <v>17577.91375</v>
       </c>
       <c r="I26" s="44" t="e">
         <f>C9*E26/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="J26" s="44">
-        <f>F26-G26-H26</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K26" s="44"/>
       <c r="L26" s="45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M26" s="45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="N26" s="44">
         <f>C7*E26/100</f>
-        <v>10157.91375</v>
+        <v>7477.867095999999</v>
       </c>
       <c r="O26" s="44">
-        <f>C$10*E26/100</f>
-        <v>7420</v>
-      </c>
-      <c r="P26" s="45">
         <f t="shared" si="1"/>
-        <v>17577.91375</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>3710</v>
+      </c>
+      <c r="P26" s="77">
+        <f t="shared" si="4"/>
+        <v>11187.867095999998</v>
+      </c>
+      <c r="Q26" s="78">
+        <f t="shared" si="5"/>
+        <v>11523.503108879999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7">
         <v>17</v>
       </c>
       <c r="B27" s="52" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C27" s="64" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D27" s="64"/>
       <c r="E27" s="43">
         <v>0.51</v>
       </c>
       <c r="F27" s="58">
-        <v>43534.28174727202</v>
+        <v>55474.322412053785</v>
       </c>
       <c r="G27" s="44">
         <v>0</v>
@@ -2268,145 +2346,157 @@
         <v>#VALUE!</v>
       </c>
       <c r="J27" s="44">
-        <f>F27-G27-H27</f>
-        <v>43534.28174727202</v>
+        <f t="shared" si="8"/>
+        <v>55474.322412053785</v>
       </c>
       <c r="K27" s="44"/>
       <c r="L27" s="45">
-        <f t="shared" si="2"/>
-        <v>3482.7425397817615</v>
+        <f t="shared" si="6"/>
+        <v>4437.9457929643031</v>
       </c>
       <c r="M27" s="45">
-        <f t="shared" si="3"/>
-        <v>47017.024287053784</v>
+        <f t="shared" si="7"/>
+        <v>59912.268205018088</v>
       </c>
       <c r="N27" s="44">
         <f>C7*E27/100</f>
-        <v>4887.2981250000003</v>
+        <v>3597.8417159999995</v>
       </c>
       <c r="O27" s="44">
-        <f>C$10*E27/100</f>
-        <v>3570</v>
-      </c>
-      <c r="P27" s="45">
         <f t="shared" si="1"/>
-        <v>55474.322412053785</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1785</v>
+      </c>
+      <c r="P27" s="77">
+        <f t="shared" si="4"/>
+        <v>65295.109921018091</v>
+      </c>
+      <c r="Q27" s="78">
+        <f t="shared" si="5"/>
+        <v>67253.963218648627</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7">
         <v>18</v>
       </c>
       <c r="B28" s="52" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C28" s="64" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D28" s="64"/>
       <c r="E28" s="43">
         <v>0.27</v>
       </c>
       <c r="F28" s="58">
-        <v>3379.3733790000006</v>
+        <v>4477.3931250000005</v>
       </c>
       <c r="G28" s="44">
         <v>0</v>
       </c>
       <c r="H28" s="69">
         <f>F28</f>
-        <v>3379.3733790000006</v>
+        <v>4477.3931250000005</v>
       </c>
       <c r="I28" s="44" t="e">
         <f>C9*E28/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="J28" s="44">
-        <f>F28-G28-H28</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K28" s="44"/>
       <c r="L28" s="45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M28" s="45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="N28" s="44">
         <f>C7*E28/100</f>
-        <v>2587.3931250000005</v>
+        <v>1904.7397319999998</v>
       </c>
       <c r="O28" s="44">
-        <f>C$10*E28/100</f>
-        <v>1890</v>
-      </c>
-      <c r="P28" s="45">
         <f t="shared" si="1"/>
-        <v>4477.3931250000005</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>945</v>
+      </c>
+      <c r="P28" s="77">
+        <f t="shared" si="4"/>
+        <v>2849.739732</v>
+      </c>
+      <c r="Q28" s="78">
+        <f t="shared" si="5"/>
+        <v>2935.2319239600001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="41"/>
       <c r="B29" s="52" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C29" s="65" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D29" s="65"/>
       <c r="E29" s="47">
         <v>1.82</v>
       </c>
       <c r="F29" s="59">
-        <v>22779.479813999998</v>
+        <v>30180.946250000001</v>
       </c>
       <c r="G29" s="44">
         <v>0</v>
       </c>
       <c r="H29" s="69">
         <f>F29</f>
-        <v>22779.479813999998</v>
+        <v>30180.946250000001</v>
       </c>
       <c r="I29" s="48"/>
       <c r="J29" s="44">
-        <f>F29-G29-H29</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="K29" s="48"/>
       <c r="L29" s="45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="M29" s="45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="N29" s="48">
         <f>C7*E29/100</f>
-        <v>17440.946250000001</v>
+        <v>12839.356712000001</v>
       </c>
       <c r="O29" s="44">
-        <f>C$10*E29/100</f>
-        <v>12740</v>
-      </c>
-      <c r="P29" s="45">
         <f t="shared" si="1"/>
-        <v>30180.946250000001</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" s="2" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="80" t="s">
+        <v>6370</v>
+      </c>
+      <c r="P29" s="77">
+        <f t="shared" si="4"/>
+        <v>19209.356712000001</v>
+      </c>
+      <c r="Q29" s="78">
+        <f t="shared" si="5"/>
+        <v>19785.63741336</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" s="2" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A30" s="88" t="s">
         <v>14</v>
       </c>
-      <c r="B30" s="81"/>
-      <c r="C30" s="81"/>
+      <c r="B30" s="89"/>
+      <c r="C30" s="89"/>
       <c r="D30" s="61"/>
       <c r="E30" s="42"/>
       <c r="F30" s="54">
         <f>SUM(F12:F29)</f>
-        <v>2552081.8371776491</v>
+        <v>3111391.7901135953</v>
       </c>
       <c r="G30" s="54">
         <f>SUM(G12:G29)</f>
@@ -2414,160 +2504,170 @@
       </c>
       <c r="H30" s="62">
         <f>SUM(H12:H29)</f>
-        <v>1206620.6889243203</v>
+        <v>1278402.3537500002</v>
       </c>
       <c r="I30" s="54"/>
       <c r="J30" s="62">
         <f>SUM(J12:J29)</f>
-        <v>1395461.1482533291</v>
+        <v>1832989.4363635955</v>
       </c>
       <c r="K30" s="54"/>
       <c r="L30" s="68">
         <f>L12+L13+L14+L15+L16+L17+L18+L19+L20+L21+L22+L23+L24+L25+L26+L27+L28+L29</f>
-        <v>107636.89186026633</v>
+        <v>146639.15490908764</v>
       </c>
       <c r="M30" s="55"/>
       <c r="N30" s="70">
         <f>SUM(N12:N29)</f>
-        <v>958293.74999999965</v>
+        <v>705459.15999999992</v>
       </c>
       <c r="O30" s="56">
         <f>SUM(O12:O29)</f>
-        <v>700000</v>
+        <v>350000</v>
       </c>
       <c r="P30" s="57">
         <f>SUM(P16:P29) +P15+P14+P13+P12</f>
-        <v>3111391.7901135944</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" ht="34.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="77" t="s">
-        <v>54</v>
-      </c>
-      <c r="C31" s="78"/>
-      <c r="D31" s="78"/>
-      <c r="E31" s="78"/>
-      <c r="F31" s="78"/>
-      <c r="G31" s="78"/>
-      <c r="H31" s="78"/>
-      <c r="I31" s="78"/>
-      <c r="J31" s="78"/>
-      <c r="K31" s="78"/>
-      <c r="L31" s="78"/>
-      <c r="M31" s="78"/>
-      <c r="N31" s="78"/>
-      <c r="O31" s="78"/>
-      <c r="P31" s="79"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+        <v>3035087.751272683</v>
+      </c>
+      <c r="Q30" s="57">
+        <f>SUM(Q16:Q29) +Q15+Q14+Q13+Q12</f>
+        <v>3126140.3838108638</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="34.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="85" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" s="86"/>
+      <c r="D31" s="86"/>
+      <c r="E31" s="86"/>
+      <c r="F31" s="86"/>
+      <c r="G31" s="86"/>
+      <c r="H31" s="86"/>
+      <c r="I31" s="86"/>
+      <c r="J31" s="86"/>
+      <c r="K31" s="86"/>
+      <c r="L31" s="86"/>
+      <c r="M31" s="86"/>
+      <c r="N31" s="86"/>
+      <c r="O31" s="86"/>
+      <c r="P31" s="86"/>
+      <c r="Q31" s="87"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="E32" s="40"/>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
       <c r="J32" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K32" s="4"/>
     </row>
-    <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="71"/>
-      <c r="C33" s="71"/>
-      <c r="D33" s="71"/>
-      <c r="E33" s="71"/>
-      <c r="F33" s="71"/>
-      <c r="G33" s="71"/>
-      <c r="H33" s="71"/>
-      <c r="I33" s="71"/>
-      <c r="J33" s="71"/>
-      <c r="K33" s="71"/>
-      <c r="L33" s="71"/>
-      <c r="M33" s="71"/>
-      <c r="N33" s="71"/>
-      <c r="O33" s="71"/>
-      <c r="P33" s="71"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B34" s="71"/>
-      <c r="C34" s="71"/>
-      <c r="D34" s="71"/>
-      <c r="E34" s="71"/>
-      <c r="F34" s="71"/>
-      <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
-      <c r="I34" s="71"/>
-      <c r="J34" s="71"/>
-      <c r="K34" s="71"/>
-      <c r="L34" s="71"/>
-      <c r="M34" s="71"/>
-      <c r="N34" s="71"/>
-      <c r="O34" s="71"/>
-      <c r="P34" s="71"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B35" s="71"/>
-      <c r="C35" s="71"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="71"/>
-      <c r="F35" s="71"/>
-      <c r="G35" s="71"/>
-      <c r="H35" s="71"/>
-      <c r="I35" s="71"/>
-      <c r="J35" s="71"/>
-      <c r="K35" s="71"/>
-      <c r="L35" s="71"/>
-      <c r="M35" s="71"/>
-      <c r="N35" s="71"/>
-      <c r="O35" s="71"/>
-      <c r="P35" s="71"/>
-    </row>
-    <row r="36" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B36" s="71"/>
-      <c r="C36" s="71"/>
-      <c r="D36" s="71"/>
-      <c r="E36" s="71"/>
-      <c r="F36" s="71"/>
-      <c r="G36" s="71"/>
-      <c r="H36" s="71"/>
-      <c r="I36" s="71"/>
-      <c r="J36" s="71"/>
-      <c r="K36" s="71"/>
-      <c r="L36" s="71"/>
-      <c r="M36" s="71"/>
-      <c r="N36" s="71"/>
-      <c r="O36" s="71"/>
-      <c r="P36" s="71"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B37" s="71"/>
-      <c r="C37" s="71"/>
-      <c r="D37" s="71"/>
-      <c r="E37" s="71"/>
-      <c r="F37" s="71"/>
-      <c r="G37" s="71"/>
-      <c r="H37" s="71"/>
-      <c r="I37" s="71"/>
-      <c r="J37" s="71"/>
-      <c r="K37" s="71"/>
-      <c r="L37" s="71"/>
-      <c r="M37" s="71"/>
-      <c r="N37" s="71"/>
-      <c r="O37" s="71"/>
-      <c r="P37" s="71"/>
+    <row r="33" spans="2:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="79"/>
+      <c r="C33" s="79"/>
+      <c r="D33" s="79"/>
+      <c r="E33" s="79"/>
+      <c r="F33" s="79"/>
+      <c r="G33" s="79"/>
+      <c r="H33" s="79"/>
+      <c r="I33" s="79"/>
+      <c r="J33" s="79"/>
+      <c r="K33" s="79"/>
+      <c r="L33" s="79"/>
+      <c r="M33" s="79"/>
+      <c r="N33" s="79"/>
+      <c r="O33" s="79"/>
+      <c r="P33" s="79"/>
+      <c r="Q33" s="79"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B34" s="79"/>
+      <c r="C34" s="79"/>
+      <c r="D34" s="79"/>
+      <c r="E34" s="79"/>
+      <c r="F34" s="79"/>
+      <c r="G34" s="79"/>
+      <c r="H34" s="79"/>
+      <c r="I34" s="79"/>
+      <c r="J34" s="79"/>
+      <c r="K34" s="79"/>
+      <c r="L34" s="79"/>
+      <c r="M34" s="79"/>
+      <c r="N34" s="79"/>
+      <c r="O34" s="79"/>
+      <c r="P34" s="79"/>
+      <c r="Q34" s="79"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B35" s="79"/>
+      <c r="C35" s="79"/>
+      <c r="D35" s="79"/>
+      <c r="E35" s="79"/>
+      <c r="F35" s="79"/>
+      <c r="G35" s="79"/>
+      <c r="H35" s="79"/>
+      <c r="I35" s="79"/>
+      <c r="J35" s="79"/>
+      <c r="K35" s="79"/>
+      <c r="L35" s="79"/>
+      <c r="M35" s="79"/>
+      <c r="N35" s="79"/>
+      <c r="O35" s="79"/>
+      <c r="P35" s="79"/>
+      <c r="Q35" s="79"/>
+    </row>
+    <row r="36" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B36" s="79"/>
+      <c r="C36" s="79"/>
+      <c r="D36" s="79"/>
+      <c r="E36" s="79"/>
+      <c r="F36" s="79"/>
+      <c r="G36" s="79"/>
+      <c r="H36" s="79"/>
+      <c r="I36" s="79"/>
+      <c r="J36" s="79"/>
+      <c r="K36" s="79"/>
+      <c r="L36" s="79"/>
+      <c r="M36" s="79"/>
+      <c r="N36" s="79"/>
+      <c r="O36" s="79"/>
+      <c r="P36" s="79"/>
+      <c r="Q36" s="79"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B37" s="79"/>
+      <c r="C37" s="79"/>
+      <c r="D37" s="79"/>
+      <c r="E37" s="79"/>
+      <c r="F37" s="79"/>
+      <c r="G37" s="79"/>
+      <c r="H37" s="79"/>
+      <c r="I37" s="79"/>
+      <c r="J37" s="79"/>
+      <c r="K37" s="79"/>
+      <c r="L37" s="79"/>
+      <c r="M37" s="79"/>
+      <c r="N37" s="79"/>
+      <c r="O37" s="79"/>
+      <c r="P37" s="79"/>
+      <c r="Q37" s="79"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="B33:P37"/>
-    <mergeCell ref="L4:P4"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="B31:P31"/>
+    <mergeCell ref="B33:Q37"/>
+    <mergeCell ref="L4:Q4"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="B31:Q31"/>
     <mergeCell ref="A30:C30"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="L5" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="92" fitToWidth="0" orientation="landscape" r:id="rId2"/>
+  <pageSetup paperSize="5" fitToWidth="0" orientation="landscape" r:id="rId2"/>
   <drawing r:id="rId3"/>
 </worksheet>
 </file>
@@ -2585,7 +2685,7 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" s="33">
         <v>0</v>
@@ -2593,7 +2693,7 @@
     </row>
     <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3" s="33">
         <v>0</v>
@@ -2610,13 +2710,13 @@
         <v>3</v>
       </c>
       <c r="D4" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="30" t="s">
+      <c r="F4" s="32" t="s">
         <v>23</v>
-      </c>
-      <c r="F4" s="32" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2627,7 +2727,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D5" s="36">
         <v>7.9899999999999999E-2</v>
@@ -2649,7 +2749,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D6" s="36">
         <v>6.0499999999999998E-2</v>
@@ -2671,7 +2771,7 @@
         <v>8</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" s="36">
         <v>6.0199999999999997E-2</v>
@@ -2689,13 +2789,13 @@
       <c r="A8" s="7">
         <v>4</v>
       </c>
-      <c r="B8" s="85" t="s">
+      <c r="B8" s="93" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="82">
+        <v>30</v>
+      </c>
+      <c r="D8" s="90">
         <v>7.6300000000000007E-2</v>
       </c>
       <c r="E8" s="5">
@@ -2711,11 +2811,11 @@
       <c r="A9" s="7">
         <v>5</v>
       </c>
-      <c r="B9" s="83"/>
+      <c r="B9" s="91"/>
       <c r="C9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" s="83"/>
+        <v>31</v>
+      </c>
+      <c r="D9" s="91"/>
       <c r="E9" s="5">
         <f>B2*D9/100</f>
         <v>0</v>
@@ -2733,7 +2833,7 @@
         <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D10" s="36">
         <v>6.0499999999999998E-2</v>
@@ -2755,7 +2855,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D11" s="36">
         <v>6.0199999999999997E-2</v>
@@ -2777,7 +2877,7 @@
         <v>11</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D12" s="36">
         <v>7.6300000000000007E-2</v>
@@ -2799,7 +2899,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D13" s="36">
         <v>6.0499999999999998E-2</v>
@@ -2818,10 +2918,10 @@
         <v>10</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="D14" s="36">
         <v>6.0199999999999997E-2</v>
@@ -2840,10 +2940,10 @@
         <v>11</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="86" t="s">
-        <v>40</v>
+        <v>37</v>
+      </c>
+      <c r="C15" s="94" t="s">
+        <v>39</v>
       </c>
       <c r="D15" s="36">
         <v>0.21199999999999999</v>
@@ -2862,9 +2962,9 @@
         <v>12</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="87" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="95" t="s">
         <v>13</v>
       </c>
       <c r="D16" s="36">
@@ -2884,10 +2984,10 @@
         <v>13</v>
       </c>
       <c r="B17" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="D17" s="36">
         <v>6.5199999999999994E-2</v>
@@ -2906,10 +3006,10 @@
         <v>14</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="D18" s="36">
         <v>1.18E-2</v>
@@ -2928,10 +3028,10 @@
         <v>15</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>46</v>
       </c>
       <c r="D19" s="36">
         <v>1.17E-2</v>
@@ -2950,10 +3050,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D20" s="36">
         <v>1.06E-2</v>
@@ -2972,10 +3072,10 @@
         <v>17</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D21" s="36">
         <v>5.1000000000000004E-3</v>
@@ -2994,10 +3094,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D22" s="36">
         <v>2.7000000000000001E-3</v>
@@ -3012,11 +3112,11 @@
       </c>
     </row>
     <row r="23" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A23" s="84" t="s">
+      <c r="A23" s="92" t="s">
         <v>14</v>
       </c>
-      <c r="B23" s="84"/>
-      <c r="C23" s="84"/>
+      <c r="B23" s="92"/>
+      <c r="C23" s="92"/>
       <c r="D23" s="23">
         <f>SUM(D5:D22)</f>
         <v>0.98180000000000023</v>
